--- a/music/Song Attributions.xlsx
+++ b/music/Song Attributions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="33">
   <si>
     <t>Song</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>link</t>
+  </si>
+  <si>
+    <t>Changes made</t>
   </si>
   <si>
     <t>Entering Graciously</t>
@@ -42,12 +45,84 @@
       <t>Entering Graciously</t>
     </r>
   </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>Biggie</t>
+  </si>
+  <si>
+    <t>ALBIS</t>
+  </si>
+  <si>
+    <t>Bet On It</t>
+  </si>
+  <si>
+    <t>Silent Partner</t>
+  </si>
+  <si>
+    <t>Licensed under Creative Commons Attribution-NoDerivs 2.0 Generic (CC BY-ND 2.0)</t>
+  </si>
+  <si>
+    <t>Restored Soul</t>
+  </si>
+  <si>
+    <t>Keffy Kay</t>
+  </si>
+  <si>
+    <t>Licensed under Creative Commons Attribution 3.0 Unported (CC BY 3.0)</t>
+  </si>
+  <si>
+    <t>Ersatz Bossa</t>
+  </si>
+  <si>
+    <t>John Deley and the 41 Players</t>
+  </si>
+  <si>
+    <t>Airport Lounge</t>
+  </si>
+  <si>
+    <t>Disco Ultralounge by Kevin MacLeod</t>
+  </si>
+  <si>
+    <t>Licensed under a Creative Commons Attribution license (CC BY 4.0)</t>
+  </si>
+  <si>
+    <t>Quirky and Happy</t>
+  </si>
+  <si>
+    <t>Rise of the Evil</t>
+  </si>
+  <si>
+    <t>Ally Calvine</t>
+  </si>
+  <si>
+    <t>The Gates of Mazrogyl</t>
+  </si>
+  <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>Vibe Tracks (LIMO Recording Studio)</t>
+  </si>
+  <si>
+    <t>Sunset Beach</t>
+  </si>
+  <si>
+    <t>Scandinavianz</t>
+  </si>
+  <si>
+    <t>Deep Hat</t>
+  </si>
+  <si>
+    <t>Stockholm</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -63,6 +138,16 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
@@ -89,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -99,7 +184,13 @@
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -321,7 +412,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="15.5"/>
     <col customWidth="1" min="2" max="2" width="19.75"/>
-    <col customWidth="1" min="3" max="3" width="57.88"/>
+    <col customWidth="1" min="3" max="3" width="68.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -337,25 +428,245 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="D2"/>
+    <hyperlink r:id="rId1" ref="C2"/>
+    <hyperlink r:id="rId2" ref="D2"/>
+    <hyperlink r:id="rId3" ref="C3"/>
+    <hyperlink r:id="rId4" ref="D3"/>
+    <hyperlink r:id="rId5" ref="C4"/>
+    <hyperlink r:id="rId6" ref="D4"/>
+    <hyperlink r:id="rId7" ref="C5"/>
+    <hyperlink r:id="rId8" ref="D5"/>
+    <hyperlink r:id="rId9" ref="C6"/>
+    <hyperlink r:id="rId10" ref="D6"/>
+    <hyperlink r:id="rId11" ref="B7"/>
+    <hyperlink r:id="rId12" ref="C7"/>
+    <hyperlink r:id="rId13" ref="D7"/>
+    <hyperlink r:id="rId14" ref="C8"/>
+    <hyperlink r:id="rId15" ref="D8"/>
+    <hyperlink r:id="rId16" ref="C9"/>
+    <hyperlink r:id="rId17" ref="D9"/>
+    <hyperlink r:id="rId18" ref="C10"/>
+    <hyperlink r:id="rId19" ref="D10"/>
+    <hyperlink r:id="rId20" ref="D11"/>
+    <hyperlink r:id="rId21" ref="D12"/>
+    <hyperlink r:id="rId22" ref="D13"/>
+    <hyperlink r:id="rId23" ref="D14"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId24"/>
 </worksheet>
 </file>